--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>156</v>
       </c>
       <c r="T2" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>903</v>
+        <v>925</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>755</v>
+        <v>774</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>71</v>
       </c>
       <c r="T9" t="n">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>153</v>
       </c>
       <c r="T3" t="n">
-        <v>1292</v>
+        <v>1298</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3186,10 +3186,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>45</v>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M3" t="n">
         <v>25</v>
@@ -896,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="T3" t="n">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -956,6 +956,7 @@
 Gransotdyna
 Grantaggsvamp
 Gropticka
+Grönhjon
 Gullpudra
 Gulsparv
 Jungfrulin
@@ -1116,10 +1117,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1343,10 +1344,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1570,10 +1571,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1600,7 +1601,7 @@
         <v>19</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
         <v>10</v>
@@ -1615,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R6" t="n">
         <v>15</v>
       </c>
       <c r="S6" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="T6" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1656,6 +1657,7 @@
 Enkelbeckasin
 Entita
 Etternässla
+Fjällig taggsvamp s.str.
 Grönsångare
 Gullpudra
 Gulsparv
@@ -1785,10 +1787,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1993,10 +1995,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2176,10 +2178,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2354,10 +2356,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2526,10 +2528,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2696,10 +2698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2865,10 +2867,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3025,10 +3027,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3186,10 +3188,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3342,10 +3344,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3496,10 +3498,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3634,10 +3636,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3766,10 +3768,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3889,10 +3891,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4013,10 +4015,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4133,10 +4135,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4244,10 +4246,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
         <v>108</v>
       </c>
       <c r="T6" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4246,10 +4246,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ramsjöns naturreservat</t>
+          <t>Högstaskogens naturreservat</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -609,45 +609,309 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>280.8</v>
+        <v>415</v>
       </c>
       <c r="J2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="n">
         <v>53</v>
       </c>
       <c r="M2" t="n">
+        <v>25</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>83</v>
+      </c>
+      <c r="R2" t="n">
+        <v>30</v>
+      </c>
+      <c r="S2" t="n">
+        <v>157</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1302</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Brödtaggsvamp
+Koppartaggsvamp
+Raggtaggsvamp
+Skogsalm
+Brunfläckig pärlemorfjäril
+Garnlav
+Goliatmusseron
+Grangråticka
+Gränsticka
+Grönfink
+Gul taggsvamp
+Hasselsnok
+Hussvala
+Igelkott
+Kejsarskivling
+Knärot
+Lakritsmusseron
+Läderdoftande fingersvamp
+Mindre bastardsvärmare
+Ramaria ossolana
+Ringlav
+Rotfingersvamp
+Ryl
+Silverblåvinge
+Skrovlig taggsvamp
+Starrgräsfjäril
+Tallgråticka
+Violettkantad guldvinge
+Ängsblåvinge
+Apelsinticka
+Backstarr
+Blek fingersvamp
+Blå taggsvamp
+Dofttaggsvamp
+Dropptaggsvamp
+Dunmossa
+Duvhök
+Enkelbeckasin
+Entita
+Fjällig taggsvamp s.str.
+Gransotdyna
+Grantaggsvamp
+Gropticka
+Grönhjon
+Gullpudra
+Gulsparv
+Jungfrulin
+Kandelabersvamp
+Kantdyna
+Kattfotslav
+Kötticka
+Loppstarr
+Lunglav
+Mindre hackspett
+Mindre tåtelsmygare
+Motaggsvamp
+Nordfladdermus
+Orange taggsvamp
+Rynkskinn
+Rödvingetrast
+Skarp dropptaggsvamp
+Skogshare
+Skuggblåslav
+Storgröe
+Svartvit taggsvamp
+Svedjenäva
+Såpfingersvamp
+Tallfingersvamp
+Tallkötticka
+Tallriska
+Talltaggsvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vedskivlav
+Vedtrappmossa
+Vintertagging
+Vit vedfingersvamp
+Vågticka
+Vårärt
+Älg
+Björksplintborre
+Blodticka
+Blomkålssvamp
+Blåmossa
+Blåsfliksmossa
+Brandticka
+Bronshjon
+Bågpraktmossa
+Bårdlav
+Dvärghäxört
+Dvärgkällmossa
+Flagellkvastmossa
+Granbarkgnagare
+Granbräken
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Guldkremla
+Igelkottsröksvamp
+Korallrot
+Mandelriska
+Maskfingersvamp
+Mindre märgborre
+Mörk husmossa
+Nästlav
+Platt fjädermossa
+Plattlummer
+Rävticka
+Rödgul trumpetsvamp
+Skogsbräsma
+Skogshakmossa
+Sotlav
+Sotriska
+Stenporella
+Stor aspticka
+Stor revmossa
+Strutbräken
+Svart trolldruva
+Svavelriska
+Toppvaxing
+Vedticka
+Västlig hakmossa
+Vätteros
+Åttafläckig praktbagge
+Ögonpyrola
+Blåsippa
+Brudborste
+Ekbräken
+Mattlummer
+Nattskärra
+Repestarr
+Spillkråka
+Tjäder
+Tofsmes
+Gröngöling
+Grönsiska
+Kungsfågel
+Näktergal
+Större vattensalamander
+Trana
+Törnskata
+Huggorm
+Kopparödla
+Mindre vattensalamander
+Skogsödla
+Vanlig groda
+Vanlig padda
+Vanlig snok
+Fläcknycklar
+Myggblomster
+Ängsnycklar
+Lopplummer (aggregat)
+Revlummer
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Högstaskogens naturreservat artfynd.xlsx", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Högstaskogens naturreservat karta.png", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Högstaskogens naturreservat georefererad karta.tif", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Högstaskogens naturreservat karta knärot.png", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Högstaskogens naturreservat FSC-klagomål.docx", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Högstaskogens naturreservat FSC-klagomål mail.docx", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Högstaskogens naturreservat tillsynsbegäran.docx", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Högstaskogens naturreservat tillsynsbegäran mail.docx", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Högstaskogens naturreservat prioriterade fågelarter.docx", "Högstaskogens naturreservat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ramsjöns naturreservat</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46277</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>40</v>
+      </c>
+      <c r="K3" t="n">
+        <v>46</v>
+      </c>
+      <c r="L3" t="n">
+        <v>53</v>
+      </c>
+      <c r="M3" t="n">
         <v>22</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>78</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R3" t="n">
         <v>25</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S3" t="n">
         <v>156</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T3" t="n">
         <v>776</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Klätt
 Koppartaggsvamp
@@ -807,301 +1071,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Ramsjöns naturreservat artfynd.xlsx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Ramsjöns naturreservat karta.png", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Ramsjöns naturreservat georefererad karta.tif", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Ramsjöns naturreservat karta knärot.png", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Ramsjöns naturreservat FSC-klagomål.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Ramsjöns naturreservat FSC-klagomål mail.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Ramsjöns naturreservat tillsynsbegäran.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Ramsjöns naturreservat tillsynsbegäran mail.docx", "Ramsjöns naturreservat")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Ramsjöns naturreservat prioriterade fågelarter.docx", "Ramsjöns naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Högstaskogens naturreservat</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46276</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>415</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41</v>
-      </c>
-      <c r="K3" t="n">
-        <v>45</v>
-      </c>
-      <c r="L3" t="n">
-        <v>51</v>
-      </c>
-      <c r="M3" t="n">
-        <v>25</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>81</v>
-      </c>
-      <c r="R3" t="n">
-        <v>30</v>
-      </c>
-      <c r="S3" t="n">
-        <v>154</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Brödtaggsvamp
-Koppartaggsvamp
-Raggtaggsvamp
-Skogsalm
-Brunfläckig pärlemorfjäril
-Garnlav
-Goliatmusseron
-Grangråticka
-Gränsticka
-Grönfink
-Gul taggsvamp
-Hasselsnok
-Hussvala
-Igelkott
-Kejsarskivling
-Knärot
-Lakritsmusseron
-Läderdoftande fingersvamp
-Mindre bastardsvärmare
-Ramaria ossolana
-Ringlav
-Rotfingersvamp
-Ryl
-Silverblåvinge
-Skrovlig taggsvamp
-Starrgräsfjäril
-Tallgråticka
-Violettkantad guldvinge
-Ängsblåvinge
-Apelsinticka
-Backstarr
-Blek fingersvamp
-Blå taggsvamp
-Dofttaggsvamp
-Dropptaggsvamp
-Dunmossa
-Duvhök
-Enkelbeckasin
-Entita
-Fjällig taggsvamp s.str.
-Gransotdyna
-Grantaggsvamp
-Gropticka
-Grönhjon
-Gullpudra
-Gulsparv
-Jungfrulin
-Kandelabersvamp
-Kattfotslav
-Kötticka
-Loppstarr
-Lunglav
-Mindre hackspett
-Mindre tåtelsmygare
-Motaggsvamp
-Nordfladdermus
-Orange taggsvamp
-Rynkskinn
-Rödvingetrast
-Skarp dropptaggsvamp
-Skogshare
-Storgröe
-Svartvit taggsvamp
-Svedjenäva
-Såpfingersvamp
-Tallfingersvamp
-Tallkötticka
-Tallriska
-Talltaggsvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vedskivlav
-Vedtrappmossa
-Vintertagging
-Vit vedfingersvamp
-Vågticka
-Vårärt
-Älg
-Björksplintborre
-Blodticka
-Blomkålssvamp
-Blåmossa
-Blåsfliksmossa
-Brandticka
-Bronshjon
-Bågpraktmossa
-Bårdlav
-Dvärghäxört
-Dvärgkällmossa
-Flagellkvastmossa
-Granbarkgnagare
-Granbräken
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Guldkremla
-Igelkottsröksvamp
-Korallrot
-Mandelriska
-Maskfingersvamp
-Mindre märgborre
-Mörk husmossa
-Nästlav
-Platt fjädermossa
-Plattlummer
-Rävticka
-Rödgul trumpetsvamp
-Skogsbräsma
-Skogshakmossa
-Sotlav
-Sotriska
-Stenporella
-Stor aspticka
-Stor revmossa
-Strutbräken
-Svart trolldruva
-Svavelriska
-Toppvaxing
-Vedticka
-Västlig hakmossa
-Vätteros
-Åttafläckig praktbagge
-Ögonpyrola
-Blåsippa
-Brudborste
-Mattlummer
-Nattskärra
-Repestarr
-Spillkråka
-Tjäder
-Tofsmes
-Gröngöling
-Grönsiska
-Kungsfågel
-Näktergal
-Större vattensalamander
-Trana
-Törnskata
-Huggorm
-Kopparödla
-Mindre vattensalamander
-Skogsödla
-Vanlig groda
-Vanlig padda
-Vanlig snok
-Fläcknycklar
-Myggblomster
-Ängsnycklar
-Lopplummer (aggregat)
-Revlummer
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Högstaskogens naturreservat artfynd.xlsx", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Högstaskogens naturreservat karta.png", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Högstaskogens naturreservat georefererad karta.tif", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Z3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Högstaskogens naturreservat karta knärot.png", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Högstaskogens naturreservat FSC-klagomål.docx", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Högstaskogens naturreservat FSC-klagomål mail.docx", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Högstaskogens naturreservat tillsynsbegäran.docx", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Högstaskogens naturreservat tillsynsbegäran mail.docx", "Högstaskogens naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Högstaskogens naturreservat prioriterade fågelarter.docx", "Högstaskogens naturreservat")</f>
         <v/>
       </c>
     </row>
@@ -1117,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1344,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1393,7 +1396,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>927</v>
+        <v>932</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1571,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1787,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1836,7 +1839,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1995,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2178,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2356,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2528,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2698,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2867,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3027,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3188,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3344,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3498,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3636,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3768,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3891,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4015,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4135,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4246,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>157</v>
       </c>
       <c r="T2" t="n">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>157</v>
       </c>
       <c r="T2" t="n">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>157</v>
       </c>
       <c r="T2" t="n">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>156</v>
       </c>
       <c r="T3" t="n">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>157</v>
       </c>
       <c r="T2" t="n">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>943</v>
+        <v>960</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>71</v>
       </c>
       <c r="T9" t="n">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3030,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4138,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>58</v>
       </c>
       <c r="L4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
         <v>10</v>
@@ -1160,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R4" t="n">
         <v>15</v>
       </c>
       <c r="S4" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T4" t="n">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1195,6 +1195,7 @@
 Berggräsfjäril
 Crepis tectorum subsp. tectorum
 Drillsnäppa
+Dropptaggsvamp
 Ekticka
 Fjällig taggsvamp s.str.
 Flattoppad klubbsvamp
@@ -1347,10 +1348,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1396,7 +1397,7 @@
         <v>120</v>
       </c>
       <c r="T5" t="n">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1574,10 +1575,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1790,10 +1791,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1839,7 +1840,7 @@
         <v>101</v>
       </c>
       <c r="T7" t="n">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1998,10 +1999,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2181,10 +2182,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2359,10 +2360,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2408,7 +2409,7 @@
         <v>69</v>
       </c>
       <c r="T10" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2531,10 +2532,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2701,10 +2702,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2870,10 +2871,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3030,10 +3031,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3191,10 +3192,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3347,10 +3348,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3501,10 +3502,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3639,10 +3640,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3771,10 +3772,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3894,10 +3895,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4018,10 +4019,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4138,10 +4139,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4249,10 +4250,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1791,10 +1791,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2351,70 +2351,244 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Lervassa träsk naturreservat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>37</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
+        <v>71</v>
+      </c>
+      <c r="T10" t="n">
+        <v>792</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp
+Koppartaggsvamp
+Bredbrämad bastardsvärmare
+Garnlav
+Goliatmusseron
+Gränsticka
+Grönfink
+Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Skrovlig taggsvamp
+Barrviolspindling
+Blå taggsvamp
+Dofttaggsvamp
+Dropptaggsvamp
+Enkelbeckasin
+Fjällig taggsvamp s.str.
+Grönhjon
+Gulsparv
+Kandelabersvamp
+Kattfotslav
+Kortskaftad ärgspik
+Kötticka
+Motaggsvamp
+Orange taggsvamp
+Phellodon aquiloniniger
+Reliktbock
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vedskivlav
+Vedtrappmossa
+Vintertagging
+Vitplätt
+Vågticka
+Björksplintborre
+Blomkålssvamp
+Blåmossa
+Bronshjon
+Flagellkvastmossa
+Granbarkgnagare
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Skogshakmossa
+Stekelbock
+Stor aspticka
+Stubbspretmossa
+Thomsons trägnagare
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Linnea
+Spillkråka
+Tjäder
+Fiskgjuse
+Gröngöling
+Havsörn
+Kungsfågel
+Orre
+Huggorm
+Kopparödla
+Mindre vattensalamander
+Vanlig groda
+Vanlig padda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Lervassa träsk naturreservat artfynd.xlsx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Norra skogen</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D11" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Stockholms län</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Haninge</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>403.2</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" t="n">
         <v>26</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" t="n">
         <v>25</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>25</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N11" t="n">
         <v>1</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>29</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>4</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S11" t="n">
         <v>69</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" t="n">
         <v>426</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Ejder
 Grangråticka
@@ -2487,206 +2661,36 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norra skogen artfynd.xlsx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norra skogen karta.png", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norra skogen georefererad karta.tif", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norra skogen FSC-klagomål.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norra skogen FSC-klagomål mail.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norra skogen tillsynsbegäran.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norra skogen tillsynsbegäran mail.docx", "Norra skogen")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norra skogen prioriterade fågelarter.docx", "Norra skogen")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Lervassa träsk naturreservat</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46285</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>20</v>
-      </c>
-      <c r="K11" t="n">
-        <v>15</v>
-      </c>
-      <c r="L11" t="n">
-        <v>27</v>
-      </c>
-      <c r="M11" t="n">
-        <v>8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>37</v>
-      </c>
-      <c r="R11" t="n">
-        <v>10</v>
-      </c>
-      <c r="S11" t="n">
-        <v>67</v>
-      </c>
-      <c r="T11" t="n">
-        <v>781</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Knölig taggsvamp
-Koppartaggsvamp
-Bredbrämad bastardsvärmare
-Garnlav
-Goliatmusseron
-Gränsticka
-Grönfink
-Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Skrovlig taggsvamp
-Barrviolspindling
-Blå taggsvamp
-Dofttaggsvamp
-Dropptaggsvamp
-Enkelbeckasin
-Fjällig taggsvamp s.str.
-Grönhjon
-Gulsparv
-Kandelabersvamp
-Kattfotslav
-Kortskaftad ärgspik
-Kötticka
-Motaggsvamp
-Orange taggsvamp
-Phellodon aquiloniniger
-Reliktbock
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vedskivlav
-Vedtrappmossa
-Vintertagging
-Vitplätt
-Vågticka
-Björksplintborre
-Blomkålssvamp
-Blåmossa
-Bronshjon
-Granbarkgnagare
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Stekelbock
-Stor aspticka
-Stubbspretmossa
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Spillkråka
-Tjäder
-Fiskgjuse
-Gröngöling
-Havsörn
-Kungsfågel
-Orre
-Huggorm
-Kopparödla
-Mindre vattensalamander
-Vanlig groda
-Vanlig padda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Lervassa träsk naturreservat artfynd.xlsx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
     </row>
@@ -2702,10 +2706,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2871,10 +2875,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3031,10 +3035,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3192,10 +3196,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3348,10 +3352,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3502,10 +3506,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3640,10 +3644,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3772,10 +3776,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3895,10 +3899,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4019,10 +4023,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4139,10 +4143,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4250,10 +4254,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1111,70 +1111,305 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Norrbytorps naturreservat utökat</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>41</v>
+      </c>
+      <c r="K4" t="n">
+        <v>33</v>
+      </c>
+      <c r="L4" t="n">
+        <v>46</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>67</v>
+      </c>
+      <c r="R4" t="n">
+        <v>21</v>
+      </c>
+      <c r="S4" t="n">
+        <v>128</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1033</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Brödtaggsvamp
+Koppartaggsvamp
+Svartoxe
+Garnlav
+Goliatmusseron
+Gränsticka
+Gul taggsvamp
+Hasselsnok
+Jättemusseron
+Knärot
+Lakritsmusseron
+Lappuggla
+Liten hornflikmossa
+Mindre bastardsvärmare
+Mjölkörtsspinnare
+Ostticka
+Ringlav
+Rotfingersvamp
+Sexfläckig bastardsvärmare
+Skrovlig taggsvamp
+Tallgråticka
+Adam och eva
+Apelsinticka
+Blå taggsvamp
+Blåhake
+Brunklöver
+Brunlångöra
+Dofttaggsvamp
+Dropptaggsvamp
+Duvhök
+Fjällig taggsvamp s.str.
+Fyrflikig jordstjärna
+Gelatinfingersvamp
+Grantaggsvamp
+Gullklöver
+Gulsparv
+Jungfrulin
+Järnsparv
+Kandelabersvamp
+Koralltaggsvamp
+Krusfrö
+Lunglav
+Mindre hackspett
+Motaggsvamp
+Nordfladdermus
+Orange taggsvamp
+Reliktbock
+Rosenticka
+Rynkskinn
+Skarp dropptaggsvamp
+Skogsklocka
+Svartvit taggsvamp
+Sågtandad mycelbagge
+Tallfingersvamp
+Tallkötticka
+Talltagel
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vaddporing
+Veckticka
+Vedskivlav
+Vedtrappmossa
+Vintertagging
+Vit vedfingersvamp
+Vågticka
+Aspvedborre
+Björksplintborre
+Blodticka
+Blomkålssvamp
+Blåmossa
+Brandticka
+Bronshjon
+Dorcatoma dresdensis
+Flagellkvastmossa
+Fällmossa
+Granbarkgnagare
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Jättesvampmal
+Korallrot
+Mindre märgborre
+Nästlav
+Platt fjädermossa
+Plattlummer
+Rostfläck
+Rödgul trumpetsvamp
+Spindelblomster
+Stor aspticka
+Stubbspretmossa
+Thomsons trägnagare
+Thymalus limbatus
+Trådticka
+Vanlig flatbagge
+Vedticka
+Västlig hakmossa
+Vågbandad barkbock
+Zontaggsvamp
+Krushättemossa
+Linnea
+Mattlummer
+Nattskärra
+Spillkråka
+Tallört (aggregat)
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Gröngöling
+Grönsiska
+Havsörn
+Kungsfågel
+Större brunfladdermus
+Trana
+Trollpipistrell
+Törnskata
+Vattenfladdermus
+Åkergroda
+Huggorm
+Kopparödla
+Mindre vattensalamander
+Vanlig groda
+Vanlig padda
+Vanlig snok
+Fläcknycklar
+Nattviol
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat utökat artfynd.xlsx", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat utökat karta.png", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat utökat georefererad karta.tif", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="Z4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat utökat karta knärot.png", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat utökat FSC-klagomål.docx", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat utökat FSC-klagomål mail.docx", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat utökat tillsynsbegäran.docx", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat utökat tillsynsbegäran mail.docx", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat utökat prioriterade fågelarter.docx", "Norrbytorps naturreservat utökat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Ornös nordspets</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="D5" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Stockholms län</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Haninge</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>450.6</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>25</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>58</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>35</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>10</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N5" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>51</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>15</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S5" t="n">
         <v>121</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>451</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Almlav
 Ask
@@ -1299,114 +1534,113 @@
 Gullviva</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Ornös nordspets artfynd.xlsx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Ornös nordspets karta.png", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Ornös nordspets georefererad karta.tif", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="Z4">
+      <c r="Z5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Ornös nordspets karta knärot.png", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Ornös nordspets FSC-klagomål.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Ornös nordspets FSC-klagomål mail.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Ornös nordspets tillsynsbegäran.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Ornös nordspets tillsynsbegäran mail.docx", "Ornös nordspets")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Ornös nordspets prioriterade fågelarter.docx", "Ornös nordspets")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Norrbytorps naturreservat utökat</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Norrbytorps naturreservat</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="D6" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Stockholms län</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Haninge</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>35</v>
-      </c>
-      <c r="K5" t="n">
-        <v>32</v>
-      </c>
-      <c r="L5" t="n">
-        <v>44</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="I6" t="n">
+        <v>159.7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>38</v>
+      </c>
+      <c r="K6" t="n">
+        <v>26</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>58</v>
+      </c>
+      <c r="R6" t="n">
         <v>18</v>
       </c>
-      <c r="N5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>65</v>
-      </c>
-      <c r="R5" t="n">
-        <v>21</v>
-      </c>
-      <c r="S5" t="n">
-        <v>120</v>
-      </c>
-      <c r="T5" t="n">
-        <v>965</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="S6" t="n">
+        <v>109</v>
+      </c>
+      <c r="T6" t="n">
+        <v>882</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Brödtaggsvamp
 Koppartaggsvamp
-Svartoxe
 Garnlav
 Goliatmusseron
 Gränsticka
@@ -1416,10 +1650,8 @@
 Knärot
 Lakritsmusseron
 Lappuggla
-Liten hornflikmossa
 Mindre bastardsvärmare
 Mjölkörtsspinnare
-Ostticka
 Ringlav
 Rotfingersvamp
 Sexfläckig bastardsvärmare
@@ -1430,6 +1662,7 @@
 Blå taggsvamp
 Blåhake
 Brunklöver
+Brunlångöra
 Dofttaggsvamp
 Dropptaggsvamp
 Duvhök
@@ -1447,36 +1680,29 @@
 Lunglav
 Mindre hackspett
 Motaggsvamp
+Nordfladdermus
 Orange taggsvamp
 Reliktbock
-Rosenticka
-Rynkskinn
 Skarp dropptaggsvamp
 Skogsklocka
 Svartvit taggsvamp
-Sågtandad mycelbagge
 Tallfingersvamp
-Tallkötticka
 Talltagel
 Tallticka
 Talltita
 Tjockfotad fingersvamp
 Ullticka
 Vaddporing
-Veckticka
 Vedskivlav
 Vedtrappmossa
 Vintertagging
-Vit vedfingersvamp
 Vågticka
-Aspvedborre
 Björksplintborre
-Blodticka
 Blomkålssvamp
 Blåmossa
 Brandticka
 Bronshjon
-Dorcatoma dresdensis
+Flagellkvastmossa
 Fällmossa
 Granbarkgnagare
 Grovticka
@@ -1486,21 +1712,18 @@
 Korallrot
 Mindre märgborre
 Nästlav
-Platt fjädermossa
 Plattlummer
 Rostfläck
 Rödgul trumpetsvamp
 Spindelblomster
-Stor aspticka
 Stubbspretmossa
 Thomsons trägnagare
-Thymalus limbatus
 Trådticka
-Vanlig flatbagge
 Vedticka
 Västlig hakmossa
 Vågbandad barkbock
 Zontaggsvamp
+Krushättemossa
 Linnea
 Mattlummer
 Nattskärra
@@ -1508,12 +1731,14 @@
 Tallört (aggregat)
 Tjäder
 Tofsmes
+Dvärgpipistrell
 Gröngöling
-Grönsiska
 Havsörn
-Kungsfågel
+Större brunfladdermus
 Trana
+Trollpipistrell
 Törnskata
+Vattenfladdermus
 Åkergroda
 Huggorm
 Kopparödla
@@ -1522,119 +1747,118 @@
 Vanlig padda
 Vanlig snok
 Fläcknycklar
-Nattviol
 Revlummer</t>
         </is>
       </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat utökat artfynd.xlsx", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat utökat karta.png", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat utökat georefererad karta.tif", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="Z5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat utökat karta knärot.png", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat utökat FSC-klagomål.docx", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat utökat FSC-klagomål mail.docx", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat utökat tillsynsbegäran.docx", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat utökat tillsynsbegäran mail.docx", "Norrbytorps naturreservat utökat")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat utökat prioriterade fågelarter.docx", "Norrbytorps naturreservat utökat")</f>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat artfynd.xlsx", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat karta.png", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat georefererad karta.tif", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat karta knärot.png", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat FSC-klagomål.docx", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat FSC-klagomål mail.docx", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat tillsynsbegäran.docx", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat tillsynsbegäran mail.docx", "Norrbytorps naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat prioriterade fågelarter.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Skäggsmoskogens naturreservat</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D7" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Stockholms län</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Haninge</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kommuner</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" t="n">
         <v>185.8</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>65</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>19</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>37</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>10</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N7" t="n">
         <v>5</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>53</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>15</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>108</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>267</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Grusnejlika
 Havstrut
@@ -1746,244 +1970,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Skäggsmoskogens naturreservat karta.png", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Skäggsmoskogens naturreservat georefererad karta.tif", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Skäggsmoskogens naturreservat FSC-klagomål.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Skäggsmoskogens naturreservat FSC-klagomål mail.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Skäggsmoskogens naturreservat tillsynsbegäran.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Skäggsmoskogens naturreservat tillsynsbegäran mail.docx", "Skäggsmoskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Skäggsmoskogens naturreservat prioriterade fågelarter.docx", "Skäggsmoskogens naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Norrbytorps naturreservat</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>159.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>32</v>
-      </c>
-      <c r="K7" t="n">
-        <v>25</v>
-      </c>
-      <c r="L7" t="n">
-        <v>38</v>
-      </c>
-      <c r="M7" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>101</v>
-      </c>
-      <c r="T7" t="n">
-        <v>814</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Brödtaggsvamp
-Koppartaggsvamp
-Garnlav
-Goliatmusseron
-Gränsticka
-Gul taggsvamp
-Hasselsnok
-Jättemusseron
-Knärot
-Lakritsmusseron
-Lappuggla
-Mindre bastardsvärmare
-Mjölkörtsspinnare
-Ringlav
-Rotfingersvamp
-Sexfläckig bastardsvärmare
-Skrovlig taggsvamp
-Tallgråticka
-Adam och eva
-Apelsinticka
-Blå taggsvamp
-Blåhake
-Brunklöver
-Dofttaggsvamp
-Dropptaggsvamp
-Duvhök
-Fjällig taggsvamp s.str.
-Fyrflikig jordstjärna
-Gelatinfingersvamp
-Grantaggsvamp
-Gullklöver
-Gulsparv
-Jungfrulin
-Järnsparv
-Kandelabersvamp
-Koralltaggsvamp
-Krusfrö
-Lunglav
-Mindre hackspett
-Motaggsvamp
-Orange taggsvamp
-Reliktbock
-Skarp dropptaggsvamp
-Skogsklocka
-Svartvit taggsvamp
-Tallfingersvamp
-Talltagel
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vaddporing
-Vedskivlav
-Vedtrappmossa
-Vintertagging
-Vågticka
-Björksplintborre
-Blomkålssvamp
-Blåmossa
-Brandticka
-Bronshjon
-Fällmossa
-Granbarkgnagare
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Jättesvampmal
-Korallrot
-Mindre märgborre
-Nästlav
-Plattlummer
-Rostfläck
-Rödgul trumpetsvamp
-Spindelblomster
-Stubbspretmossa
-Thomsons trägnagare
-Trådticka
-Vedticka
-Västlig hakmossa
-Vågbandad barkbock
-Zontaggsvamp
-Linnea
-Mattlummer
-Nattskärra
-Spillkråka
-Tallört (aggregat)
-Tjäder
-Tofsmes
-Gröngöling
-Havsörn
-Trana
-Törnskata
-Åkergroda
-Huggorm
-Kopparödla
-Mindre vattensalamander
-Vanlig groda
-Vanlig padda
-Vanlig snok
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat artfynd.xlsx", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat karta.png", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat georefererad karta.tif", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat karta knärot.png", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat FSC-klagomål.docx", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat FSC-klagomål mail.docx", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat tillsynsbegäran.docx", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat tillsynsbegäran mail.docx", "Norrbytorps naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat prioriterade fågelarter.docx", "Norrbytorps naturreservat")</f>
         <v/>
       </c>
     </row>
@@ -1999,10 +2015,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2173,7 +2189,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tyresta naturreservat med skogsbruk</t>
+          <t>Lervassa träsk naturreservat</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2182,10 +2198,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2198,19 +2214,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>237.7</v>
+        <v>168.3</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -2225,18 +2241,194 @@
         <v>37</v>
       </c>
       <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
+        <v>73</v>
+      </c>
+      <c r="T9" t="n">
+        <v>820</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knölig taggsvamp
+Koppartaggsvamp
+Bredbrämad bastardsvärmare
+Garnlav
+Goliatmusseron
+Gränsticka
+Grönfink
+Mindre bastardsvärmare
+Sexfläckig bastardsvärmare
+Skrovlig taggsvamp
+Barrviolspindling
+Blå taggsvamp
+Dofttaggsvamp
+Dropptaggsvamp
+Enkelbeckasin
+Fjällig taggsvamp s.str.
+Grönhjon
+Gulsparv
+Kandelabersvamp
+Kattfotslav
+Kortskaftad ärgspik
+Kötticka
+Motaggsvamp
+Orange taggsvamp
+Phellodon aquiloniniger
+Reliktbock
+Skarp dropptaggsvamp
+Svartvit taggsvamp
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vedskivlav
+Vedtrappmossa
+Vintertagging
+Vitplätt
+Vågticka
+Björksplintborre
+Blomkålssvamp
+Blåmossa
+Bronshjon
+Flagellkvastmossa
+Granbarkgnagare
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Mindre märgborre
+Rödgul trumpetsvamp
+Skogshakmossa
+Stekelbock
+Stor aspticka
+Stubbspretmossa
+Thomsons trägnagare
+Trådticka
+Vedticka
+Vågbandad barkbock
+Blåsippa
+Linnea
+Spillkråka
+Tjäder
+Tofsmes
+Fiskgjuse
+Gröngöling
+Havsörn
+Kungsfågel
+Orre
+Huggorm
+Kopparödla
+Mindre vattensalamander
+Vanlig groda
+Vanlig padda
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Lervassa träsk naturreservat artfynd.xlsx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tyresta naturreservat med skogsbruk</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>237.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26</v>
+      </c>
+      <c r="K10" t="n">
+        <v>16</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>37</v>
+      </c>
+      <c r="R10" t="n">
         <v>12</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>71</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>549</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Brandnäva
 Koppartaggsvamp
@@ -2311,214 +2503,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Tyresta naturreservat med skogsbruk karta.png", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tyresta naturreservat med skogsbruk georefererad karta.tif", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tyresta naturreservat med skogsbruk karta knärot.png", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tyresta naturreservat med skogsbruk FSC-klagomål.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tyresta naturreservat med skogsbruk FSC-klagomål mail.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tyresta naturreservat med skogsbruk tillsynsbegäran.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tyresta naturreservat med skogsbruk tillsynsbegäran mail.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tyresta naturreservat med skogsbruk prioriterade fågelarter.docx", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lervassa träsk naturreservat</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20</v>
-      </c>
-      <c r="K10" t="n">
-        <v>18</v>
-      </c>
-      <c r="L10" t="n">
-        <v>27</v>
-      </c>
-      <c r="M10" t="n">
-        <v>8</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>37</v>
-      </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" t="n">
-        <v>71</v>
-      </c>
-      <c r="T10" t="n">
-        <v>792</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knölig taggsvamp
-Koppartaggsvamp
-Bredbrämad bastardsvärmare
-Garnlav
-Goliatmusseron
-Gränsticka
-Grönfink
-Mindre bastardsvärmare
-Sexfläckig bastardsvärmare
-Skrovlig taggsvamp
-Barrviolspindling
-Blå taggsvamp
-Dofttaggsvamp
-Dropptaggsvamp
-Enkelbeckasin
-Fjällig taggsvamp s.str.
-Grönhjon
-Gulsparv
-Kandelabersvamp
-Kattfotslav
-Kortskaftad ärgspik
-Kötticka
-Motaggsvamp
-Orange taggsvamp
-Phellodon aquiloniniger
-Reliktbock
-Skarp dropptaggsvamp
-Svartvit taggsvamp
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vedskivlav
-Vedtrappmossa
-Vintertagging
-Vitplätt
-Vågticka
-Björksplintborre
-Blomkålssvamp
-Blåmossa
-Bronshjon
-Flagellkvastmossa
-Granbarkgnagare
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Mindre märgborre
-Rödgul trumpetsvamp
-Skogshakmossa
-Stekelbock
-Stor aspticka
-Stubbspretmossa
-Thomsons trägnagare
-Vedticka
-Vågbandad barkbock
-Blåsippa
-Linnea
-Spillkråka
-Tjäder
-Fiskgjuse
-Gröngöling
-Havsörn
-Kungsfågel
-Orre
-Huggorm
-Kopparödla
-Mindre vattensalamander
-Vanlig groda
-Vanlig padda
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Lervassa träsk naturreservat artfynd.xlsx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
     </row>
@@ -2534,10 +2552,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2706,10 +2724,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2875,10 +2893,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3035,10 +3053,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3196,10 +3214,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3352,10 +3370,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3377,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M16" t="n">
         <v>8</v>
@@ -3392,16 +3410,16 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R16" t="n">
         <v>9</v>
       </c>
       <c r="S16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T16" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -3421,6 +3439,7 @@
 Apelsinticka
 Blå taggsvamp
 Brunklöver
+Dofttaggsvamp
 Dropptaggsvamp
 Gullklöver
 Krusfrö
@@ -3506,10 +3525,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3644,10 +3663,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3776,10 +3795,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3899,10 +3918,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4023,10 +4042,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4143,10 +4162,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4254,10 +4273,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1033</v>
+        <v>1049</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>109</v>
       </c>
       <c r="T6" t="n">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>185.8</v>
       </c>
       <c r="J7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K7" t="n">
         <v>19</v>
@@ -1850,10 +1850,10 @@
         <v>15</v>
       </c>
       <c r="S7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T7" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1936,6 +1936,7 @@
 Kärrfibbla
 Mattlummer
 Spillkråka
+Stjärtmes
 Tallbit
 Tjäder
 Tofsmes
@@ -2015,10 +2016,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2198,10 +2199,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2374,10 +2375,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2423,7 +2424,7 @@
         <v>71</v>
       </c>
       <c r="T10" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2552,10 +2553,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2577,7 +2578,7 @@
         <v>25</v>
       </c>
       <c r="L11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
@@ -2592,16 +2593,16 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R11" t="n">
         <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="T11" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -2632,6 +2633,7 @@
 Silltrut
 Skarp dropptaggsvamp
 Sädesärla
+Såpfingersvamp
 Sårläka
 Tallticka
 Ullticka
@@ -2724,10 +2726,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2893,10 +2895,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3053,10 +3055,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3214,10 +3216,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3370,10 +3372,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3525,10 +3527,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3663,10 +3665,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3795,10 +3797,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3918,10 +3920,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4042,10 +4044,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4162,10 +4164,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4273,10 +4275,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1049</v>
+        <v>1081</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6" t="n">
         <v>40</v>
@@ -1629,10 +1629,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1698,6 +1698,7 @@
 Vintertagging
 Vågticka
 Björksplintborre
+Blodticka
 Blomkålssvamp
 Blåmossa
 Brandticka
@@ -1799,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2016,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2199,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2248,7 +2249,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2375,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2397,7 +2398,7 @@
         <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>25</v>
@@ -2421,10 +2422,10 @@
         <v>12</v>
       </c>
       <c r="S10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2470,6 +2471,7 @@
 Älg
 Blodticka
 Blomkålssvamp
+Blåmossa
 Brandticka
 Grovticka
 Grön sköldmossa
@@ -2553,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2726,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2895,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3055,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3216,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3372,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3527,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3665,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3797,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3920,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4044,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4164,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4275,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1081</v>
+        <v>1101</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>568</v>
+        <v>595</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>156</v>
       </c>
       <c r="T3" t="n">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>157</v>
       </c>
       <c r="T2" t="n">
-        <v>1335</v>
+        <v>1361</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1108</v>
+        <v>1137</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>935</v>
+        <v>964</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1137</v>
+        <v>1151</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>964</v>
+        <v>978</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1151</v>
+        <v>1167</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>128</v>
       </c>
       <c r="T4" t="n">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>110</v>
       </c>
       <c r="T6" t="n">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
         <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2728,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2897,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3529,10 +3529,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4046,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4166,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>157</v>
       </c>
       <c r="T2" t="n">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>194.4</v>
       </c>
       <c r="J4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" t="n">
         <v>33</v>
@@ -1166,10 +1166,10 @@
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="T4" t="n">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1276,6 +1276,7 @@
 Västlig hakmossa
 Vågbandad barkbock
 Zontaggsvamp
+Blåsippa
 Krushättemossa
 Linnea
 Mattlummer
@@ -1355,10 +1356,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1583,10 +1584,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1602,7 +1603,7 @@
         <v>159.7</v>
       </c>
       <c r="J6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K6" t="n">
         <v>27</v>
@@ -1629,10 +1630,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T6" t="n">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1724,6 +1725,7 @@
 Västlig hakmossa
 Vågbandad barkbock
 Zontaggsvamp
+Blåsippa
 Krushättemossa
 Linnea
 Mattlummer
@@ -1800,10 +1802,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2017,10 +2019,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2200,10 +2202,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2376,10 +2378,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2425,7 +2427,7 @@
         <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2555,10 +2557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2728,10 +2730,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2897,10 +2899,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3057,10 +3059,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3209,7 +3211,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tutvikskogens naturreservat</t>
+          <t>Norrbytorps naturreservat söder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3218,10 +3220,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3234,22 +3236,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>194.2</v>
+        <v>128</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -3258,21 +3260,179 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="R15" t="n">
         <v>9</v>
       </c>
       <c r="S15" t="n">
+        <v>51</v>
+      </c>
+      <c r="T15" t="n">
+        <v>314</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Hornuggla
+Brunfläckig pärlemorfjäril
+Garnlav
+Goliatmusseron
+Igelkott
+Jättemusseron
+Knärot
+Lakritsmusseron
+Skrovlig taggsvamp
+Adam och eva
+Apelsinticka
+Blå taggsvamp
+Brunklöver
+Dofttaggsvamp
+Dropptaggsvamp
+Gullklöver
+Krusfrö
+Motaggsvamp
+Orange taggsvamp
+Skogshare
+Skogsklocka
+Svartvit taggsvamp
+Tallkötticka
+Tallriska
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vintertagging
+Blodticka
+Blåmossa
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Mindre märgborre
+Plattlummer
+Vedticka
+Blåsippa
+Mattlummer
+Nattskärra
+Spillkråka
+Tallbit
+Tofsmes
+Havsörn
+Kungsfågel
+Huggorm
+Vanlig padda
+Fläcknycklar
+Nattviol
+Lopplummer (aggregat)
+Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat söder artfynd.xlsx", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat söder karta.png", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat söder georefererad karta.tif", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat söder karta knärot.png", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat söder FSC-klagomål.docx", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat söder FSC-klagomål mail.docx", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat söder tillsynsbegäran.docx", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat söder tillsynsbegäran mail.docx", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat söder prioriterade fågelarter.docx", "Norrbytorps naturreservat söder")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tutvikskogens naturreservat</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>194.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>14</v>
+      </c>
+      <c r="L16" t="n">
+        <v>16</v>
+      </c>
+      <c r="M16" t="n">
+        <v>9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>25</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9</v>
+      </c>
+      <c r="S16" t="n">
         <v>49</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>352</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Goliatmusseron
@@ -3325,195 +3485,40 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Tutvikskogens naturreservat artfynd.xlsx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Tutvikskogens naturreservat karta.png", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tutvikskogens naturreservat georefererad karta.tif", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tutvikskogens naturreservat karta knärot.png", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tutvikskogens naturreservat FSC-klagomål.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tutvikskogens naturreservat FSC-klagomål mail.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tutvikskogens naturreservat tillsynsbegäran.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tutvikskogens naturreservat tillsynsbegäran mail.docx", "Tutvikskogens naturreservat")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tutvikskogens naturreservat prioriterade fågelarter.docx", "Tutvikskogens naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Norrbytorps naturreservat söder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>128</v>
-      </c>
-      <c r="J16" t="n">
-        <v>18</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20</v>
-      </c>
-      <c r="M16" t="n">
-        <v>8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>29</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>48</v>
-      </c>
-      <c r="T16" t="n">
-        <v>287</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Hornuggla
-Brunfläckig pärlemorfjäril
-Garnlav
-Goliatmusseron
-Igelkott
-Jättemusseron
-Knärot
-Lakritsmusseron
-Skrovlig taggsvamp
-Adam och eva
-Apelsinticka
-Blå taggsvamp
-Brunklöver
-Dofttaggsvamp
-Dropptaggsvamp
-Gullklöver
-Krusfrö
-Motaggsvamp
-Orange taggsvamp
-Skogshare
-Skogsklocka
-Svartvit taggsvamp
-Tallkötticka
-Tallriska
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vintertagging
-Blodticka
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Mindre märgborre
-Plattlummer
-Vedticka
-Blåsippa
-Mattlummer
-Nattskärra
-Tallbit
-Havsörn
-Kungsfågel
-Huggorm
-Vanlig padda
-Fläcknycklar
-Nattviol
-Lopplummer (aggregat)
-Äkta lopplummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Norrbytorps naturreservat söder artfynd.xlsx", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Norrbytorps naturreservat söder karta.png", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Norrbytorps naturreservat söder georefererad karta.tif", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Norrbytorps naturreservat söder karta knärot.png", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Norrbytorps naturreservat söder FSC-klagomål.docx", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Norrbytorps naturreservat söder FSC-klagomål mail.docx", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Norrbytorps naturreservat söder tillsynsbegäran.docx", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Norrbytorps naturreservat söder tillsynsbegäran mail.docx", "Norrbytorps naturreservat söder")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Norrbytorps naturreservat söder prioriterade fågelarter.docx", "Norrbytorps naturreservat söder")</f>
         <v/>
       </c>
     </row>
@@ -3529,10 +3534,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3667,10 +3672,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3799,10 +3804,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3922,10 +3927,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4046,10 +4051,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4166,10 +4171,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4277,10 +4282,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3220,10 +3220,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3804,10 +3804,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3927,10 +3927,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1160,16 +1160,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R4" t="n">
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="T4" t="n">
-        <v>1169</v>
+        <v>1216</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1243,6 +1243,7 @@
 Vintertagging
 Vit vedfingersvamp
 Vågticka
+Porodaedalea chrysoloma
 Aspvedborre
 Björksplintborre
 Blodticka
@@ -1277,6 +1278,7 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
+Ekbräken
 Krushättemossa
 Linnea
 Mattlummer
@@ -1356,10 +1358,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1584,10 +1586,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1609,7 +1611,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M6" t="n">
         <v>16</v>
@@ -1624,16 +1626,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R6" t="n">
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="T6" t="n">
-        <v>996</v>
+        <v>1035</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1688,6 +1690,7 @@
 Skogsklocka
 Svartvit taggsvamp
 Tallfingersvamp
+Tallkötticka
 Talltagel
 Tallticka
 Talltita
@@ -1726,6 +1729,7 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
+Ekbräken
 Krushättemossa
 Linnea
 Mattlummer
@@ -1802,10 +1806,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2019,10 +2023,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2202,10 +2206,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2378,10 +2382,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2427,7 +2431,7 @@
         <v>72</v>
       </c>
       <c r="T10" t="n">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -2557,10 +2561,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2730,10 +2734,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2899,10 +2903,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3220,10 +3224,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3378,10 +3382,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3534,10 +3538,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3672,10 +3676,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3804,10 +3808,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3927,10 +3931,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4171,10 +4175,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4282,10 +4286,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>131</v>
       </c>
       <c r="T4" t="n">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>113</v>
       </c>
       <c r="T6" t="n">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lervassa träsk naturreservat</t>
+          <t>Tyresta naturreservat med skogsbruk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2222,19 +2222,19 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>168.3</v>
+        <v>237.7</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
@@ -2246,21 +2246,201 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S9" t="n">
         <v>73</v>
       </c>
       <c r="T9" t="n">
+        <v>643</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Brandnäva
+Koppartaggsvamp
+Garnlav
+Goliatmusseron
+Grangråticka
+Hasselsnok
+Jättemusseron
+Knärot
+Lakritsmusseron
+Mindre bastardsvärmare
+Rotfingersvamp
+Skrovlig taggsvamp
+Blå taggsvamp
+Dofttaggsvamp
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Fyrflikig jordstjärna
+Grantaggsvamp
+Jungfrulin
+Järnsparv
+Mindre hackspett
+Motaggsvamp
+Orange taggsvamp
+Reliktbock
+Skarp dropptaggsvamp
+Skogshare
+Svartvit taggsvamp
+Svedjenäva
+Sårläka
+Tallkötticka
+Tallticka
+Talltita
+Tjockfotad fingersvamp
+Ullticka
+Vedskivlav
+Vedtrappmossa
+Vintertagging
+Älg
+Blodticka
+Blomkålssvamp
+Blåmossa
+Brandticka
+Grovticka
+Grön sköldmossa
+Grönpyrola
+Kambräken
+Kamjordstjärna
+Korallrot
+Mindre märgborre
+Plattlummer
+Rödgul trumpetsvamp
+Spindelblomster
+Vedticka
+Vätteros
+Zontaggsvamp
+Linnea
+Mattlummer
+Nattskärra
+Spillkråka
+Tjäder
+Tofsmes
+Havsörn
+Kungsfågel
+Trädlärka
+Huggorm
+Kopparödla
+Mindre vattensalamander
+Vanlig groda
+Vanlig padda
+Vanlig snok
+Fläcknycklar
+Lopplummer (aggregat)
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Tyresta naturreservat med skogsbruk karta.png", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tyresta naturreservat med skogsbruk georefererad karta.tif", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tyresta naturreservat med skogsbruk karta knärot.png", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tyresta naturreservat med skogsbruk FSC-klagomål.docx", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tyresta naturreservat med skogsbruk FSC-klagomål mail.docx", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tyresta naturreservat med skogsbruk tillsynsbegäran.docx", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tyresta naturreservat med skogsbruk tillsynsbegäran mail.docx", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tyresta naturreservat med skogsbruk prioriterade fågelarter.docx", "Tyresta naturreservat med skogsbruk")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Lervassa träsk naturreservat</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stockholms län</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>168.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21</v>
+      </c>
+      <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
+        <v>27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>37</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
+        <v>73</v>
+      </c>
+      <c r="T10" t="n">
         <v>822</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knölig taggsvamp
 Koppartaggsvamp
@@ -2337,215 +2517,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Lervassa träsk naturreservat artfynd.xlsx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Lervassa träsk naturreservat karta.png", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Lervassa träsk naturreservat georefererad karta.tif", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Lervassa träsk naturreservat FSC-klagomål.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Lervassa träsk naturreservat FSC-klagomål mail.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Lervassa träsk naturreservat tillsynsbegäran.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Lervassa träsk naturreservat tillsynsbegäran mail.docx", "Lervassa träsk naturreservat")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Lervassa träsk naturreservat prioriterade fågelarter.docx", "Lervassa träsk naturreservat")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Tyresta naturreservat med skogsbruk</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Stockholms län</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Haninge</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>237.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>26</v>
-      </c>
-      <c r="K10" t="n">
-        <v>17</v>
-      </c>
-      <c r="L10" t="n">
-        <v>25</v>
-      </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>37</v>
-      </c>
-      <c r="R10" t="n">
-        <v>12</v>
-      </c>
-      <c r="S10" t="n">
-        <v>72</v>
-      </c>
-      <c r="T10" t="n">
-        <v>622</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Brandnäva
-Koppartaggsvamp
-Garnlav
-Goliatmusseron
-Grangråticka
-Hasselsnok
-Jättemusseron
-Knärot
-Lakritsmusseron
-Mindre bastardsvärmare
-Rotfingersvamp
-Skrovlig taggsvamp
-Blå taggsvamp
-Dofttaggsvamp
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Fyrflikig jordstjärna
-Grantaggsvamp
-Jungfrulin
-Järnsparv
-Mindre hackspett
-Motaggsvamp
-Orange taggsvamp
-Reliktbock
-Skogshare
-Svartvit taggsvamp
-Svedjenäva
-Sårläka
-Tallkötticka
-Tallticka
-Talltita
-Tjockfotad fingersvamp
-Ullticka
-Vedskivlav
-Vedtrappmossa
-Vintertagging
-Älg
-Blodticka
-Blomkålssvamp
-Blåmossa
-Brandticka
-Grovticka
-Grön sköldmossa
-Grönpyrola
-Kambräken
-Kamjordstjärna
-Korallrot
-Mindre märgborre
-Plattlummer
-Rödgul trumpetsvamp
-Spindelblomster
-Vedticka
-Vätteros
-Zontaggsvamp
-Linnea
-Mattlummer
-Nattskärra
-Spillkråka
-Tjäder
-Tofsmes
-Havsörn
-Kungsfågel
-Trädlärka
-Huggorm
-Kopparödla
-Mindre vattensalamander
-Vanlig groda
-Vanlig padda
-Vanlig snok
-Fläcknycklar
-Lopplummer (aggregat)
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/artfynd/Tyresta naturreservat med skogsbruk artfynd.xlsx", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor/Tyresta naturreservat med skogsbruk karta.png", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/kartor_geotiff/Tyresta naturreservat med skogsbruk georefererad karta.tif", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/knärot/Tyresta naturreservat med skogsbruk karta knärot.png", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomål/Tyresta naturreservat med skogsbruk FSC-klagomål.docx", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/klagomålsmail/Tyresta naturreservat med skogsbruk FSC-klagomål mail.docx", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsyn/Tyresta naturreservat med skogsbruk tillsynsbegäran.docx", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/tillsynsmail/Tyresta naturreservat med skogsbruk tillsynsbegäran mail.docx", "Tyresta naturreservat med skogsbruk")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_HANINGE_RESERVATSFORSLAG/fåglar/Tyresta naturreservat med skogsbruk prioriterade fågelarter.docx", "Tyresta naturreservat med skogsbruk")</f>
         <v/>
       </c>
     </row>
@@ -2561,10 +2562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2734,10 +2735,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2903,10 +2904,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3063,10 +3064,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3224,10 +3225,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3382,10 +3383,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3538,10 +3539,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3676,10 +3677,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3808,10 +3809,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3931,10 +3932,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4055,10 +4056,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4175,10 +4176,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4286,10 +4287,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>113</v>
       </c>
       <c r="T6" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1806,10 +1806,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T4" t="n">
-        <v>1219</v>
+        <v>1228</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1279,6 +1279,7 @@
 Zontaggsvamp
 Blåsippa
 Ekbräken
+Hultbräken
 Krushättemossa
 Linnea
 Mattlummer
@@ -1358,10 +1359,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1586,10 +1587,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" t="n">
-        <v>1037</v>
+        <v>1046</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1730,6 +1731,7 @@
 Zontaggsvamp
 Blåsippa
 Ekbräken
+Hultbräken
 Krushättemossa
 Linnea
 Mattlummer
@@ -1806,10 +1808,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2023,10 +2025,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2206,10 +2208,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>651</v>
+        <v>687</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2386,10 +2388,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2562,10 +2564,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2735,10 +2737,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2904,10 +2906,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3064,10 +3066,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3225,10 +3227,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3383,10 +3385,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3539,10 +3541,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3677,10 +3679,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3809,10 +3811,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3932,10 +3934,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4056,10 +4058,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4176,10 +4178,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4287,10 +4289,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T4" t="n">
-        <v>1228</v>
+        <v>1203</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1278,7 +1278,6 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
-Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1359,10 +1358,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1587,10 +1586,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1633,10 +1632,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T6" t="n">
-        <v>1046</v>
+        <v>1023</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1730,7 +1729,6 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
-Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1808,10 +1806,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2025,10 +2023,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2208,10 +2206,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2257,7 +2255,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2388,10 +2386,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2564,10 +2562,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2737,10 +2735,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2906,10 +2904,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3066,10 +3064,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3227,10 +3225,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3385,10 +3383,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3541,10 +3539,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3679,10 +3677,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3811,10 +3809,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3934,10 +3932,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4058,10 +4056,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4178,10 +4176,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4289,10 +4287,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>156</v>
       </c>
       <c r="T3" t="n">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1120,10 +1120,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1166,10 +1166,10 @@
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T4" t="n">
-        <v>1203</v>
+        <v>1230</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1278,6 +1278,7 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
+Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1358,10 +1359,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1586,10 +1587,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" t="n">
-        <v>1023</v>
+        <v>1047</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1729,6 +1730,7 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
+Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1806,10 +1808,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2023,10 +2025,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2206,10 +2208,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2386,10 +2388,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2562,10 +2564,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2735,10 +2737,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2904,10 +2906,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3064,10 +3066,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3225,10 +3227,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3383,10 +3385,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3539,10 +3541,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3677,10 +3679,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3809,10 +3811,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3932,10 +3934,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4056,10 +4058,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4176,10 +4178,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4287,10 +4289,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         <v>45</v>
       </c>
       <c r="L2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M2" t="n">
         <v>25</v>
@@ -633,16 +633,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R2" t="n">
         <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T2" t="n">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -715,6 +715,7 @@
 Skuggblåslav
 Storgröe
 Svartvit taggsvamp
+Svartöra
 Svedjenäva
 Såpfingersvamp
 Tallfingersvamp
@@ -857,10 +858,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -906,7 +907,7 @@
         <v>156</v>
       </c>
       <c r="T3" t="n">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1120,10 +1121,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1169,7 +1170,7 @@
         <v>132</v>
       </c>
       <c r="T4" t="n">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1359,10 +1360,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1587,10 +1588,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1808,10 +1809,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2025,10 +2026,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2208,10 +2209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2388,10 +2389,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2564,10 +2565,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2737,10 +2738,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2906,10 +2907,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3066,10 +3067,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3227,10 +3228,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3385,10 +3386,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3541,10 +3542,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3679,10 +3680,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3811,10 +3812,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3934,10 +3935,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4058,10 +4059,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4178,10 +4179,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4289,10 +4290,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>158</v>
       </c>
       <c r="T2" t="n">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>132</v>
       </c>
       <c r="T4" t="n">
-        <v>1229</v>
+        <v>1237</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>114</v>
       </c>
       <c r="T6" t="n">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3386,10 +3386,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3542,10 +3542,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -858,10 +858,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1167,10 +1167,10 @@
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="T4" t="n">
-        <v>1237</v>
+        <v>1213</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1279,7 +1279,6 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
-Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1360,10 +1359,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1588,10 +1587,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1634,10 +1633,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T6" t="n">
-        <v>1055</v>
+        <v>1032</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1731,7 +1730,6 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
-Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1809,10 +1807,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2026,10 +2024,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2209,10 +2207,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2258,7 +2256,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>700</v>
+        <v>709</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2389,10 +2387,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2565,10 +2563,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2738,10 +2736,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2907,10 +2905,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3067,10 +3065,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3228,10 +3226,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3386,10 +3384,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3542,10 +3540,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3680,10 +3678,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3812,10 +3810,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3935,10 +3933,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4059,10 +4057,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4179,10 +4177,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4290,10 +4288,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
         <v>415</v>
       </c>
       <c r="J2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
         <v>45</v>
@@ -639,10 +639,10 @@
         <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="T2" t="n">
-        <v>1363</v>
+        <v>1383</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -785,6 +785,7 @@
 Nattskärra
 Repestarr
 Spillkråka
+Stjärtmes
 Tjäder
 Tofsmes
 Gröngöling
@@ -858,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1121,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1167,10 +1168,10 @@
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T4" t="n">
-        <v>1213</v>
+        <v>1238</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1279,6 +1280,7 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
+Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1359,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1587,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1633,10 +1635,10 @@
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T6" t="n">
-        <v>1032</v>
+        <v>1055</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1730,6 +1732,7 @@
 Vågbandad barkbock
 Zontaggsvamp
 Blåsippa
+Ekbräken
 Hultbräken
 Krushättemossa
 Linnea
@@ -1807,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2024,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2207,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2256,7 +2259,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2387,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2563,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2736,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2905,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3065,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3226,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3384,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3540,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3678,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3810,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3933,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4057,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4177,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4288,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>726</v>
+        <v>742</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>132</v>
       </c>
       <c r="T4" t="n">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>742</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         <v>159</v>
       </c>
       <c r="T2" t="n">
-        <v>1383</v>
+        <v>1408</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>73</v>
       </c>
       <c r="T9" t="n">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1122,10 +1122,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1810,10 +1810,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2908,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         <v>45</v>
       </c>
       <c r="L2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M2" t="n">
         <v>25</v>
@@ -633,16 +633,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R2" t="n">
         <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="T2" t="n">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -708,6 +708,7 @@
 Motaggsvamp
 Nordfladdermus
 Orange taggsvamp
+Phellodon aquiloniniger
 Rynkskinn
 Rödvingetrast
 Skarp dropptaggsvamp
@@ -859,10 +860,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -908,7 +909,7 @@
         <v>156</v>
       </c>
       <c r="T3" t="n">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1122,10 +1123,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1147,7 +1148,7 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M4" t="n">
         <v>18</v>
@@ -1162,16 +1163,16 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R4" t="n">
         <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="T4" t="n">
-        <v>1239</v>
+        <v>1244</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1224,6 +1225,7 @@
 Motaggsvamp
 Nordfladdermus
 Orange taggsvamp
+Phellodon aquiloniniger
 Reliktbock
 Rosenticka
 Rynkskinn
@@ -1361,10 +1363,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1589,10 +1591,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1614,7 +1616,7 @@
         <v>27</v>
       </c>
       <c r="L6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M6" t="n">
         <v>16</v>
@@ -1629,16 +1631,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R6" t="n">
         <v>18</v>
       </c>
       <c r="S6" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="T6" t="n">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1688,6 +1690,7 @@
 Motaggsvamp
 Nordfladdermus
 Orange taggsvamp
+Phellodon aquiloniniger
 Reliktbock
 Skarp dropptaggsvamp
 Skogsklocka
@@ -1810,10 +1813,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2027,10 +2030,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2210,10 +2213,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2235,7 +2238,7 @@
         <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M9" t="n">
         <v>10</v>
@@ -2250,16 +2253,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R9" t="n">
         <v>12</v>
       </c>
       <c r="S9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="T9" t="n">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2289,6 +2292,7 @@
 Mindre hackspett
 Motaggsvamp
 Orange taggsvamp
+Phellodon aquiloniniger
 Reliktbock
 Skarp dropptaggsvamp
 Skogshare
@@ -2390,10 +2394,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2566,10 +2570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2739,10 +2743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2908,10 +2912,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3068,10 +3072,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3229,10 +3233,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3254,7 +3258,7 @@
         <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15" t="n">
         <v>8</v>
@@ -3269,16 +3273,16 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R15" t="n">
         <v>9</v>
       </c>
       <c r="S15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T15" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -3304,6 +3308,7 @@
 Krusfrö
 Motaggsvamp
 Orange taggsvamp
+Phellodon aquiloniniger
 Skogshare
 Skogsklocka
 Svartvit taggsvamp
@@ -3387,10 +3392,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3543,10 +3548,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3681,10 +3686,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3813,10 +3818,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3936,10 +3941,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4060,10 +4065,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4180,10 +4185,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4291,10 +4296,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>133</v>
       </c>
       <c r="T4" t="n">
-        <v>1244</v>
+        <v>1253</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>115</v>
       </c>
       <c r="T6" t="n">
-        <v>1059</v>
+        <v>1068</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>133</v>
       </c>
       <c r="T4" t="n">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>115</v>
       </c>
       <c r="T6" t="n">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4065,10 +4065,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>133</v>
       </c>
       <c r="T4" t="n">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
         <v>115</v>
       </c>
       <c r="T6" t="n">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>74</v>
       </c>
       <c r="T9" t="n">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2912,10 +2912,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>21</v>
       </c>
       <c r="M15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
@@ -3273,16 +3273,16 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="T15" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -3293,6 +3293,7 @@
 Brunfläckig pärlemorfjäril
 Garnlav
 Goliatmusseron
+Gränsticka
 Igelkott
 Jättemusseron
 Knärot
@@ -3392,10 +3393,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3548,10 +3549,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3686,10 +3687,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3818,10 +3819,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3941,10 +3942,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4065,10 +4066,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4185,10 +4186,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4296,10 +4297,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L2" t="n">
         <v>55</v>
@@ -639,10 +639,10 @@
         <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T2" t="n">
-        <v>1417</v>
+        <v>1434</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -777,6 +777,7 @@
 Vedticka
 Västlig hakmossa
 Vätteros
+Zontaggsvamp
 Åttafläckig praktbagge
 Ögonpyrola
 Blåsippa
@@ -860,10 +861,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1363,10 +1364,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1591,10 +1592,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1813,10 +1814,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2030,10 +2031,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2213,10 +2214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2394,10 +2395,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2570,10 +2571,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2743,10 +2744,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2912,10 +2913,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3072,10 +3073,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3233,10 +3234,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3393,10 +3394,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3549,10 +3550,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3687,10 +3688,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3819,10 +3820,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3942,10 +3943,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4066,10 +4067,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4186,10 +4187,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4297,10 +4298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4187,10 +4187,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
